--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fcruz\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E38C1969-2B49-40A5-A9CD-4B86A0EF8459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A6934A-3E74-4AA8-BEEA-8DA15E1DE6E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FC165004-6313-4EF9-9177-E25128C6DC1F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{FC165004-6313-4EF9-9177-E25128C6DC1F}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="89">
   <si>
     <t>DATASET</t>
   </si>
@@ -187,6 +187,126 @@
   </si>
   <si>
     <t>ModernBert-base</t>
+  </si>
+  <si>
+    <t>Matriz de confusión:</t>
+  </si>
+  <si>
+    <t>[[255  16]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [ 24  46]]</t>
+  </si>
+  <si>
+    <t>Reporte de clasificación:</t>
+  </si>
+  <si>
+    <t>Valores de precisión y recall (necesitamos recall para ajustar porcentajes)</t>
+  </si>
+  <si>
+    <t>precision</t>
+  </si>
+  <si>
+    <t>recall</t>
+  </si>
+  <si>
+    <t>f1-score</t>
+  </si>
+  <si>
+    <t>support</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>0.9140</t>
+  </si>
+  <si>
+    <t>0.9410</t>
+  </si>
+  <si>
+    <t>0.9273</t>
+  </si>
+  <si>
+    <t>Configuration</t>
+  </si>
+  <si>
+    <t>0.7419</t>
+  </si>
+  <si>
+    <t>0.6571</t>
+  </si>
+  <si>
+    <t>0.6970</t>
+  </si>
+  <si>
+    <t>accuracy</t>
+  </si>
+  <si>
+    <t>0.8827</t>
+  </si>
+  <si>
+    <t>macro</t>
+  </si>
+  <si>
+    <t>avg</t>
+  </si>
+  <si>
+    <t>0.8280</t>
+  </si>
+  <si>
+    <t>0.7991</t>
+  </si>
+  <si>
+    <t>0.8121</t>
+  </si>
+  <si>
+    <t>weighted</t>
+  </si>
+  <si>
+    <t>0.8787</t>
+  </si>
+  <si>
+    <t>0.8800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eclipse_dataset </t>
+  </si>
+  <si>
+    <t>Porcentajes actuales: {'Configuration': 35.977098426346096, 'Other': 64.0229015736539}: 100%|█████████████████████████████████████████████████████| 75366/75366 [1:31:09&lt;00:00, 13.78it/s]</t>
+  </si>
+  <si>
+    <t>Predicción completada.</t>
+  </si>
+  <si>
+    <t>Etiquetas predichas mapeadas: {1: 'Configuration', 0: 'Other'}</t>
+  </si>
+  <si>
+    <t>Resultados guardados en: data/eclipse_dataset_prediccion.csv</t>
+  </si>
+  <si>
+    <t>Resumen de Predicciones:</t>
+  </si>
+  <si>
+    <t>predicted_label_index</t>
+  </si>
+  <si>
+    <t>0    193006</t>
+  </si>
+  <si>
+    <t>1    108458</t>
+  </si>
+  <si>
+    <t>Name: count, dtype: int64</t>
+  </si>
+  <si>
+    <t>predicted_label</t>
+  </si>
+  <si>
+    <t>Other            193006</t>
+  </si>
+  <si>
+    <t>Configuration    108458</t>
   </si>
 </sst>
 </file>
@@ -672,7 +792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7318367-78E8-4EFC-885A-DEFCB9B05CF4}">
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:T58"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
@@ -680,6 +800,7 @@
     <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="25.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1051,7 +1172,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -1080,7 +1201,7 @@
         <v>1.88172043010752E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
         <v>14</v>
       </c>
@@ -1103,7 +1224,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
         <v>15</v>
       </c>
@@ -1126,7 +1247,7 @@
         <v>2.6667E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
         <v>16</v>
       </c>
@@ -1149,7 +1270,7 @@
         <v>6.6667000000000004E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
         <v>17</v>
       </c>
@@ -1178,7 +1299,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
         <v>23</v>
       </c>
@@ -1207,7 +1328,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>47</v>
       </c>
@@ -1241,8 +1362,11 @@
       <c r="K24" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="N24" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C25" t="s">
         <v>48</v>
       </c>
@@ -1271,36 +1395,217 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="N26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
       <c r="I27" s="6"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="N27" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="N28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
       <c r="I29" s="6"/>
+      <c r="N29" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="O30" t="s">
+        <v>54</v>
+      </c>
+      <c r="P30" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>56</v>
+      </c>
+      <c r="R30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="O32" t="s">
+        <v>58</v>
+      </c>
+      <c r="P32" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>60</v>
+      </c>
+      <c r="R32" t="s">
+        <v>61</v>
+      </c>
+      <c r="S32">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="N33" t="s">
+        <v>62</v>
+      </c>
+      <c r="O33" t="s">
+        <v>63</v>
+      </c>
+      <c r="P33" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>65</v>
+      </c>
+      <c r="R33">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O35" t="s">
+        <v>66</v>
+      </c>
+      <c r="P35" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q35">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O36" t="s">
+        <v>68</v>
+      </c>
+      <c r="P36" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>70</v>
+      </c>
+      <c r="R36" t="s">
+        <v>71</v>
+      </c>
+      <c r="S36" t="s">
+        <v>72</v>
+      </c>
+      <c r="T36">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O37" t="s">
+        <v>73</v>
+      </c>
+      <c r="P37" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>74</v>
+      </c>
+      <c r="R37" t="s">
+        <v>67</v>
+      </c>
+      <c r="S37" t="s">
+        <v>75</v>
+      </c>
+      <c r="T37">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
+        <v>85</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
